--- a/outputs/stock_by_brand.xlsx
+++ b/outputs/stock_by_brand.xlsx
@@ -9,9 +9,31 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ИТОГО" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО БРЕНДАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ПОЗИЦИЯМ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕ ХОДОВОЙ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ХОДОВОЙ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CELIMAX" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FARMSTAY" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROUND LAB" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MANYO" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JIGOTT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PETITFEE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETUDE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENOUGH" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VT" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JMSOLUTION" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HEIMISH" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEOPROCE" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOME BY MI" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ELIZAVECCA" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COSRX" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THE ORDINARY" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEBELAGE" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LANEIGE" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKIN1004" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EKEL" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DR. JART" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASIL" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ПОЗИЦИЯМ" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НЕ ХОДОВОЙ" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ХОДОВОЙ" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +42,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="# ##0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="# ##0"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -70,14 +93,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -577,16 +604,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -595,875 +622,640 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Наименование</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Позиций</t>
+          <t>Артикул WB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Штук на складе</t>
+          <t>Склад, шт</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Остаток, руб</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Продажи, шт/мес</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Продано за период, руб</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Деньги в неликвиде, руб</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Приход в пути, шт</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Доля остатка, %</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Запас, месяцев</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Неликвид, % остатка</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для ли</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21820</v>
+        <v>238415286</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7340</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>13087532</v>
+        <v>177.43</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3651.1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>12054154.65</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>6769421</v>
+        <v>1302336</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40008</v>
+        <v>1465.6</v>
       </c>
       <c r="I2" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>51.7</v>
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" t="n">
-        <v>18817</v>
+        <v>212889028</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>707</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7730273</v>
+        <v>201.564</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4912.1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>11094211.59</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1564082</v>
+        <v>142506</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>41.1</v>
       </c>
       <c r="I3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20.2</v>
+        <v>17.2</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (о</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>9805</v>
+        <v>212889027</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>651</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5287657</v>
+        <v>201.564</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1178.8</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3395842.04</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1112755</v>
+        <v>131218</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25380</v>
+        <v>58.9</v>
       </c>
       <c r="I4" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K4" t="n">
-        <v>21</v>
+        <v>11.1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (о</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4162</v>
+        <v>212889025</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>476</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3738266</v>
+        <v>201.564</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>591.7</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3227726.34</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1706978</v>
+        <v>95944</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I5" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>45.7</v>
+        <v>7.3</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбе</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>14799</v>
+        <v>238416010</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>344</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3616791</v>
+        <v>202.268</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1405</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2033996.76</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1601116</v>
+        <v>69580</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="I6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>44.3</v>
+        <v>2.8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ENOUGH - Collagen Moisture Foundation [Tone 21] / Тональный крем для лица с</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>6262</v>
+        <v>150925322</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>212</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3104138</v>
+        <v>242.88</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1074</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2624914.68</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>822446</v>
+        <v>51491</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>63.9</v>
       </c>
       <c r="I7" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>26.5</v>
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH - Collagen Moisture Foundation [Tone 13] / Тональный крем для лица с</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7475</v>
+        <v>150925321</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>233</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2949885</v>
+        <v>216.45</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>945.1</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2163095.93</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>50433</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>62.2</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [Tone 21] / Тональ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C9" t="n">
-        <v>11168</v>
+        <v>170198337</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>149</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1975002</v>
+        <v>304.77</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2711</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>3842377.72</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>142506</v>
+        <v>45411</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1100</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тональный крем с муцино</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1406</v>
+        <v>207796789</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>95</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1908134</v>
+        <v>245.65</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>23337</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>269.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональный крем с муцино</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1871</v>
+        <v>207796898</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>82</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>905186</v>
+        <v>270.81</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>323.3</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>650456.8099999999</v>
-      </c>
-      <c r="G11" s="2" t="n">
+        <v>22206</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t xml:space="preserve">ENOUGH - Collagen 3in1 Whitening Moisture Foundation [Tone 21] / Тональный </t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>941</v>
+        <v>151132052</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>78</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>797524</v>
+        <v>223.35</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>307849.24</v>
-      </c>
-      <c r="G12" s="2" t="n">
+        <v>17421</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t xml:space="preserve">ENOUGH - Collagen 3in1 Whitening Moisture Foundation [Tone 13] / Тональный </t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>783</v>
+        <v>151132051</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>59</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>368463</v>
+        <v>238.13</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>585452.89</v>
-      </c>
-      <c r="G13" s="2" t="n">
+        <v>14050</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [Tone 13] / Тональ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>582</v>
+        <v>170198738</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>353658</v>
+        <v>335.9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>37199</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>289697</v>
+        <v>9069</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>78.3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>81.90000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>ENOUGH - Collagen Moisture BB Cream SPF47 PA+++ [50ml] / Увлажняющий BB кре</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>599</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>235810</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>48545.82</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>235810</v>
-      </c>
+        <v>238413828</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="2" t="n">
-        <v>0</v>
+        <v>101.1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="K15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>нет себестоимости</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="7" t="n">
+        <v>11168</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="n">
+        <v>1975002</v>
+      </c>
+      <c r="F16" s="8" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COSRX</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>361</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>124119</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>106458.71</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>147</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>112588</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>96823.51999999999</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LEBELAGE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>410</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>48776</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>27924.78</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>48776</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LANEIGE</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>235</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>30752</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>99310.22</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" t="n">
-        <v>52</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>18611</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>62654.42</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>EKEL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1279</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>95840.22</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DR. JART</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>37</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MASIL</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>109</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>30660</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="G16" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>2711</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>11.0% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>1100</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1479,7 +1271,3705 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1119249556</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1469.545</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1482771</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нет данных о продажах</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1123494802</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1071.444</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>425363</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>нет данных о продажах</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="7" t="n">
+        <v>1406</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="n">
+        <v>1908134</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>1.4% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - MASK PACK BLACK [30ml*10ea] - ассорти набор 10шт в упаковке</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>214977901</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>463.2</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>481265</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>214964091</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>832</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>509.52</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>423921</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>203.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="7" t="n">
+        <v>1871</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="n">
+        <v>905186</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>323.3</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>1.8% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SP</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>207466866</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>847.528</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>797524</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>941</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="n">
+        <v>797524</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>0.9% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>214305722</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>726.85</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>298008</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным ч</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>608841921</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>166.243</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>49540</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягкая упаковка Шам</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>608837066</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>269.87</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>16192</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягкая упаковка с к</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>608624295</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>314.85</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4723</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="7" t="n">
+        <v>783</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="n">
+        <v>368463</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>0.8% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g] / Мыло для пр</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>248928046</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>549.71</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>289697</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>878.3</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>248929125</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1162.92</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>63961</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="7" t="n">
+        <v>582</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="n">
+        <v>353658</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>0.6% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIZAVECCA - Milky Piggy EGF elastic retinol [100ml] / Антивозрастной крем </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>190160008</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>602.1799999999999</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>120436</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / </t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>207796350</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>266.453</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>92992</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - Hell-Pore Galactomyces Pure Ample / Сыворотка для лица с экстр</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>206058262</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>447.64</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>22382</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="7" t="n">
+        <v>599</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="n">
+        <v>235810</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>0.6% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COSRX - Salicylic Acid Daily Gentle Cleanser [150ml] / Пенка с салициловой </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>204258828</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>343.82</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>124119</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>361</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="n">
+        <v>124119</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>0.4% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворотка для лица от прыще</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>214312385</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>722.04</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>83757</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гли</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>247275092</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>930.039</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>28831</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="n">
+        <v>112588</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>0.1% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастно</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>210575566</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>118.965</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>48776</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>410</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="n">
+        <v>48776</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>0.4% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Бренд</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Позиций</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Штук на складе</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Доля по штукам, %</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля остатка, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Продано за период, руб</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Деньги в неликвиде, руб</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Неликвид, % остатка</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21820</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>13087532</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>3651.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>12054154.65</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>6769421</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>40008</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>18817</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>7730273</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>4912.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>11094211.59</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>1564082</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9805</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5287657</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1178.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>3395842.04</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1112755</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>25380</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4162</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3738266</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>591.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>3227726.34</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1706978</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14799</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3616791</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1405</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2033996.76</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1601116</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6262</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>3104138</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1074</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>2624914.68</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>822446</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7475</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2949885</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>945.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>2163095.93</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11168</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1975002</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2711</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>3842377.72</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>142506</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1406</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1908134</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1871</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>905186</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>323.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>650456.8099999999</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>941</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>797524</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>307849.24</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>783</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>368463</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>585452.89</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>582</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>353658</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>37199</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>289697</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>599</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>235810</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>48545.82</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>235810</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COSRX</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>361</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>124119</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>106458.71</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>147</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>112588</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>96823.51999999999</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>410</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>48776</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>27924.78</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>48776</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LANEIGE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>235</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>30752</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>99310.22</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>52</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>18611</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>62654.42</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EKEL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1279</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>95840.22</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DR. JART</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>37</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MASIL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>109</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>30660</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H2:H23">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>868761530</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>130.86</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>30752</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>235</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="n">
+        <v>30752</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>0.2% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаив</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>214311963</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>404.679</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>12140</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30ml] / Увлажняюща</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>214312149</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>294.15</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="n">
+        <v>18611</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>0.1% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EKEL - Ampule Сream Сollagen [70ml] / Крем для лица ампульный с коллагеном</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>208202076</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>142.13</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1279</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="n">
+        <v>1279</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>0.0% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DR. JART - Ctrl+A Teatreatment Toner [120ml] / Тонер тоник для лица увлажня</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>199427475</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нет себестоимости</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>0.0% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MASIL - 8 Seconds Salon Hair Mask 350ml Set [350ml+8ml*2]</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>183030830</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нет себестоимости</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>0.1% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1623,7 +5113,7 @@
       <c r="J2" t="n">
         <v>437.5</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -1735,7 +5225,7 @@
       <c r="J4" t="n">
         <v>1.5</v>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -2015,7 +5505,7 @@
       <c r="J9" t="n">
         <v>12.7</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -2403,7 +5893,7 @@
       <c r="J16" t="n">
         <v>34.9</v>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -2459,7 +5949,7 @@
       <c r="J17" t="n">
         <v>22.3</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -2571,7 +6061,7 @@
       <c r="J19" t="n">
         <v>14.3</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -2683,7 +6173,7 @@
       <c r="J21" t="n">
         <v>15.4</v>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -2791,7 +6281,7 @@
       <c r="J23" t="n">
         <v>1040</v>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -2901,7 +6391,7 @@
       <c r="J25" t="n">
         <v>86.5</v>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -2955,7 +6445,7 @@
       <c r="J26" t="n">
         <v>1.6</v>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -3119,7 +6609,7 @@
       <c r="J29" t="n">
         <v>16.1</v>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -3287,7 +6777,7 @@
       <c r="J32" t="n">
         <v>14.4</v>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -3343,7 +6833,7 @@
       <c r="J33" t="n">
         <v>13.4</v>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -3399,7 +6889,7 @@
       <c r="J34" t="n">
         <v>52.7</v>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -3455,7 +6945,7 @@
       <c r="J35" t="n">
         <v>13.4</v>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -3565,7 +7055,7 @@
       <c r="J37" t="n">
         <v>1.4</v>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -3677,7 +7167,7 @@
       <c r="J39" t="n">
         <v>878.3</v>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -3787,7 +7277,7 @@
       <c r="J41" t="n">
         <v>15.4</v>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -3955,7 +7445,7 @@
       <c r="J44" t="n">
         <v>665</v>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -4177,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>продаж не было</t>
         </is>
@@ -4233,7 +7723,7 @@
       <c r="J49" t="n">
         <v>265.5</v>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -4289,7 +7779,7 @@
       <c r="J50" t="n">
         <v>1.6</v>
       </c>
-      <c r="K50" s="4" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -4401,7 +7891,7 @@
       <c r="J52" t="n">
         <v>17.2</v>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -4455,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>продаж не было</t>
         </is>
@@ -4511,7 +8001,7 @@
       <c r="J54" t="n">
         <v>1.6</v>
       </c>
-      <c r="K54" s="4" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -4677,7 +8167,7 @@
       <c r="J57" t="n">
         <v>60.6</v>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -4899,7 +8389,7 @@
       <c r="J61" t="n">
         <v>21.7</v>
       </c>
-      <c r="K61" s="3" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -5345,7 +8835,7 @@
       <c r="J69" t="n">
         <v>17.5</v>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="K69" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -5675,7 +9165,7 @@
       <c r="J75" t="n">
         <v>18.9</v>
       </c>
-      <c r="K75" s="3" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -5733,7 +9223,7 @@
       <c r="J76" t="n">
         <v>20.4</v>
       </c>
-      <c r="K76" s="3" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -5841,7 +9331,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" s="3" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>продаж не было</t>
         </is>
@@ -5951,7 +9441,7 @@
       <c r="J80" t="n">
         <v>1.4</v>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6065,7 +9555,7 @@
       <c r="J82" t="n">
         <v>0.4</v>
       </c>
-      <c r="K82" s="4" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6119,7 +9609,7 @@
       <c r="J83" t="n">
         <v>15.2</v>
       </c>
-      <c r="K83" s="3" t="inlineStr">
+      <c r="K83" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -6173,7 +9663,7 @@
       <c r="J84" t="n">
         <v>0.4</v>
       </c>
-      <c r="K84" s="4" t="inlineStr">
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6337,7 +9827,7 @@
       <c r="J87" t="n">
         <v>1.6</v>
       </c>
-      <c r="K87" s="4" t="inlineStr">
+      <c r="K87" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6391,7 +9881,7 @@
       <c r="J88" t="n">
         <v>0.9</v>
       </c>
-      <c r="K88" s="4" t="inlineStr">
+      <c r="K88" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6503,7 +9993,7 @@
       <c r="J90" t="n">
         <v>0.3</v>
       </c>
-      <c r="K90" s="4" t="inlineStr">
+      <c r="K90" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6613,7 +10103,7 @@
       <c r="J92" t="n">
         <v>0.3</v>
       </c>
-      <c r="K92" s="4" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6721,7 +10211,7 @@
       <c r="J94" t="n">
         <v>0.6</v>
       </c>
-      <c r="K94" s="4" t="inlineStr">
+      <c r="K94" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6775,7 +10265,7 @@
       <c r="J95" t="n">
         <v>0.1</v>
       </c>
-      <c r="K95" s="4" t="inlineStr">
+      <c r="K95" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -6957,7 +10447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7101,7 +10591,7 @@
       <c r="J2" t="n">
         <v>437.5</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7157,7 +10647,7 @@
       <c r="J3" t="n">
         <v>12.7</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7213,7 +10703,7 @@
       <c r="J4" t="n">
         <v>34.9</v>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7269,7 +10759,7 @@
       <c r="J5" t="n">
         <v>22.3</v>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7325,7 +10815,7 @@
       <c r="J6" t="n">
         <v>14.3</v>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7381,7 +10871,7 @@
       <c r="J7" t="n">
         <v>15.4</v>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7437,7 +10927,7 @@
       <c r="J8" t="n">
         <v>1040</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7493,7 +10983,7 @@
       <c r="J9" t="n">
         <v>86.5</v>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7547,7 +11037,7 @@
       <c r="J10" t="n">
         <v>16.1</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7603,7 +11093,7 @@
       <c r="J11" t="n">
         <v>14.4</v>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7659,7 +11149,7 @@
       <c r="J12" t="n">
         <v>13.4</v>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7715,7 +11205,7 @@
       <c r="J13" t="n">
         <v>52.7</v>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7771,7 +11261,7 @@
       <c r="J14" t="n">
         <v>13.4</v>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7827,7 +11317,7 @@
       <c r="J15" t="n">
         <v>878.3</v>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7881,7 +11371,7 @@
       <c r="J16" t="n">
         <v>15.4</v>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7937,7 +11427,7 @@
       <c r="J17" t="n">
         <v>665</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -7991,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>продаж не было</t>
         </is>
@@ -8047,7 +11537,7 @@
       <c r="J19" t="n">
         <v>265.5</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -8103,7 +11593,7 @@
       <c r="J20" t="n">
         <v>17.2</v>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -8157,7 +11647,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>продаж не было</t>
         </is>
@@ -8213,7 +11703,7 @@
       <c r="J22" t="n">
         <v>60.6</v>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -8267,7 +11757,7 @@
       <c r="J23" t="n">
         <v>21.7</v>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -8323,7 +11813,7 @@
       <c r="J24" t="n">
         <v>17.5</v>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -8379,7 +11869,7 @@
       <c r="J25" t="n">
         <v>18.9</v>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -8437,7 +11927,7 @@
       <c r="J26" t="n">
         <v>20.4</v>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -8491,7 +11981,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>продаж не было</t>
         </is>
@@ -8547,7 +12037,7 @@
       <c r="J28" t="n">
         <v>15.2</v>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>неликвид, запас больше года</t>
         </is>
@@ -8583,7 +12073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8727,7 +12217,7 @@
       <c r="J2" t="n">
         <v>1.5</v>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -8783,7 +12273,7 @@
       <c r="J3" t="n">
         <v>1.4</v>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -8839,7 +12329,7 @@
       <c r="J4" t="n">
         <v>1.6</v>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -8895,7 +12385,7 @@
       <c r="J5" t="n">
         <v>0.4</v>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -8949,7 +12439,7 @@
       <c r="J6" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9003,7 +12493,7 @@
       <c r="J7" t="n">
         <v>1.6</v>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9059,7 +12549,7 @@
       <c r="J8" t="n">
         <v>1.6</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9115,7 +12605,7 @@
       <c r="J9" t="n">
         <v>0.3</v>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9169,7 +12659,7 @@
       <c r="J10" t="n">
         <v>0.1</v>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9223,7 +12713,7 @@
       <c r="J11" t="n">
         <v>0.9</v>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9277,7 +12767,7 @@
       <c r="J12" t="n">
         <v>0.3</v>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9331,7 +12821,7 @@
       <c r="J13" t="n">
         <v>1.6</v>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9385,7 +12875,7 @@
       <c r="J14" t="n">
         <v>0.6</v>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9439,7 +12929,7 @@
       <c r="J15" t="n">
         <v>1.4</v>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>ходовой, запас кончается</t>
         </is>
@@ -9475,4 +12965,3200 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бус</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>551387355</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9493</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>563.3979999999999</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5348337</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>868516027</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>4520</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>730.246</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>3300712</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>2988.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>40008</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинол</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>551465879</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3112</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>585.3100000000001</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1821485</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>434.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды о</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>551607905</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>778.668</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1168002</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выра</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>551540924</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>611.798</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>841222</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защ</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>551392965</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>353</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>950.521</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>335534</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тон</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>551600265</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1296</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>106.634</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>138198</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>продаж не было</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнив</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>551482493</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>756.3380000000001</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>58238</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сы</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>551472457</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>840.213</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>47892</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливаю</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>551518955</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>791.538</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>18997</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона </t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>551447345</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>685.7729999999999</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>8915</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="7" t="n">
+        <v>21820</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="n">
+        <v>13087532</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>3651.1</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>21.4% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>40008</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I13">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотк</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>168956391</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>6179</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>382.536</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>2363690</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1550</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-конд</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>207475898</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3493</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>436.392</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1524317</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>207472742</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3239</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>436.392</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1413474</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шам</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>207476309</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>440.836</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1073436</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>403.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином у</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>207469760</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>474.155</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>426740</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>568.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>419630142</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>901</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>429.506</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>386985</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>202.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королев</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>169076150</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>860</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>345.224</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>296893</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>610</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с колл</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>207477077</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>532.862</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>133216</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>207476777</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>177.617</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>71757</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка р</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>212885914</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>254.903</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>39765</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>продаж не было</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr"/>
+      <c r="C12" s="7" t="n">
+        <v>18817</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="n">
+        <v>7730273</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>4912.1</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>18.5% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>437154709</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7126</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>509.509</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3630761</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1072.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>25020</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лиц</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>437242640</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1422</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>563.552</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>801371</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1123574113</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>966</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>533.423</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>515287</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>нет данных о продажах</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>437190353</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1202.256</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>311384</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица у</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>437776835</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>901.692</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>28854</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="7" t="n">
+        <v>9805</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="n">
+        <v>5287657</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1178.8</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>9.6% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>25380</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>198147185</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1355</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>989.7579999999999</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1341122</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и п</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>868700077</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>614</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1096.425</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>673205</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамин</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>198156472</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>759</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>711.513</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>540038</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>237.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с биф</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>868575374</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>813.901</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>529036</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидоба</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>198143251</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>624</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>808.874</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>504737</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1040</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очище</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>198156698</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>938.3</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>150128</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="7" t="n">
+        <v>4162</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="n">
+        <v>3738266</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>591.7</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>4.1% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I8">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозраст</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>207482718</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7463</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>222.497</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1660495</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>768.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JIGOTT - Ассорти набор масок [27ml х 15]</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>255574453</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>334.05</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>450968</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатск</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>212757456</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1414</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>291.896</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>412741</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозр</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>212760119</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1296</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>291.896</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>378297</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>207483780</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1614</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>222.497</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>359110</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="I6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозра</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>207483179</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>934</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>204.446</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>190953</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>236.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>212759698</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>291.896</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>103915</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml] / Тонер с гиалуроновой к</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>212883090</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>162.13</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>60312</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="7" t="n">
+        <v>14799</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="n">
+        <v>3616791</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1405</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>14.5% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I10">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелев</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>226115324</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>741</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>535.051</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>396473</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с з</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>226114935</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>557.876</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>295116</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для </t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>179611207</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>608</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>457.0059999999999</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>277860</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи </t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>179611231</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>641</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>423.555</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>271499</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патч</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>151175880</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>549</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>426.437</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>234114</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>200.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелев</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>151175877</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>457.0059999999999</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>228960</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрог</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>226115248</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>546.546</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>218072</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>665</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для в</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>180988755</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>406</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>535.359</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>217356</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с з</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>180711104</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>457.0059999999999</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>185087</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрог</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>226114831</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>548.394</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>179325</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>продаж не было</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маск</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>226115478</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>525.855</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>153550</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>неликвид, запас больше года</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для </t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>226115141</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>525.987</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>143594</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век </t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>180987509</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>535.359</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>108143</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрог</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>179611278</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>457.0059999999999</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>71293</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрог</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>179611304</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>457.0059999999999</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>65809</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>180992464</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>650.419</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>57887</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="7" t="n">
+        <v>6262</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="n">
+        <v>3104138</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1074</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>6.1% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I18">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул WB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Склад, шт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Себестоимость, руб</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Остаток, руб</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в бренде, %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Доля в складе, %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Продажи, шт/мес</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Запас, месяцев</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Приход в пути, шт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>151313163</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7279</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>397.133</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>2890731</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>816.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>затоварен</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка с содой для гл</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>307073881</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>292.89</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>52134</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>нормальный запас</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>154160085</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>389.99</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7020</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>ходовой, запас кончается</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО БРЕНДУ</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="7" t="n">
+        <v>7475</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="n">
+        <v>2949885</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>945.1</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>7.3% всех штук склада</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
+        <cfvo type="num" val="24"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>